--- a/Resumen/EstablecimientoSalud_resumen.xlsx
+++ b/Resumen/EstablecimientoSalud_resumen.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Resumen/EstablecimientoSalud_resumen.xlsx
+++ b/Resumen/EstablecimientoSalud_resumen.xlsx
@@ -28946,7 +28946,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>LA_OROYA</t>
+          <t>LA OROYA</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -29003,7 +29003,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>LA_OROYA</t>
+          <t>LA OROYA</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>LA_OROYA</t>
+          <t>LA OROYA</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -29107,7 +29107,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -29278,7 +29278,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -29449,7 +29449,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -29506,7 +29506,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -29620,7 +29620,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -29677,7 +29677,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -29848,7 +29848,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -30019,7 +30019,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -30076,7 +30076,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -30190,7 +30190,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -30247,7 +30247,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -30304,7 +30304,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -30418,7 +30418,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -30475,7 +30475,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -38113,7 +38113,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -38170,7 +38170,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -38227,7 +38227,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -38284,7 +38284,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -38341,7 +38341,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -38398,7 +38398,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -38455,7 +38455,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -38512,7 +38512,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -38569,7 +38569,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -38626,7 +38626,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -38683,7 +38683,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -38740,7 +38740,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -38797,7 +38797,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -38854,7 +38854,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -38911,7 +38911,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -38968,7 +38968,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -39025,7 +39025,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -39082,7 +39082,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -39139,7 +39139,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -39196,7 +39196,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -39253,7 +39253,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -39310,7 +39310,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -39367,7 +39367,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -39424,7 +39424,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -39481,7 +39481,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -39538,7 +39538,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -41310,7 +41310,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -41367,7 +41367,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -41481,7 +41481,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -41538,7 +41538,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -41595,7 +41595,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -41766,7 +41766,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -41823,7 +41823,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -41880,7 +41880,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -41937,7 +41937,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -41994,7 +41994,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -42051,7 +42051,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -42108,7 +42108,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -42165,7 +42165,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -42222,7 +42222,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -42279,7 +42279,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -42450,7 +42450,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -42507,7 +42507,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -42564,7 +42564,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -42621,7 +42621,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -42678,7 +42678,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -42735,7 +42735,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -44160,7 +44160,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -44217,7 +44217,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -44274,7 +44274,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -44331,7 +44331,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -44502,7 +44502,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -44559,7 +44559,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -44616,7 +44616,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -44730,7 +44730,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -44844,7 +44844,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -44901,7 +44901,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -44958,7 +44958,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -45015,7 +45015,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -45072,7 +45072,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -45129,7 +45129,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -45186,7 +45186,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -45243,7 +45243,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -45357,7 +45357,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -45409,7 +45409,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -45466,7 +45466,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -45523,7 +45523,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -45580,7 +45580,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -45637,7 +45637,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -45694,7 +45694,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -45751,7 +45751,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -45808,7 +45808,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -45865,7 +45865,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -45922,7 +45922,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -45979,7 +45979,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -46036,7 +46036,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -46093,7 +46093,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -46150,7 +46150,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -46207,7 +46207,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -46264,7 +46264,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -46321,7 +46321,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -46378,7 +46378,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -46435,7 +46435,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -46492,7 +46492,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -46549,7 +46549,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -46606,7 +46606,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -46663,12 +46663,12 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -46720,12 +46720,12 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -46777,12 +46777,12 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -46834,12 +46834,12 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -46891,12 +46891,12 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -46948,12 +46948,12 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -47005,12 +47005,12 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -47062,12 +47062,12 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -47119,12 +47119,12 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -47176,12 +47176,12 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -47233,12 +47233,12 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -48948,7 +48948,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -49005,7 +49005,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -49062,7 +49062,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -49119,7 +49119,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -49176,7 +49176,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -49233,7 +49233,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -49290,7 +49290,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -49347,7 +49347,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -49404,7 +49404,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -49461,7 +49461,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -49518,7 +49518,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -49575,7 +49575,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -49632,7 +49632,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -49689,7 +49689,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -49803,7 +49803,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -49860,7 +49860,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -49974,7 +49974,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -50031,7 +50031,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -50088,7 +50088,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -50202,7 +50202,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -50259,7 +50259,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -50316,7 +50316,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -50373,7 +50373,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -50430,7 +50430,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -50487,7 +50487,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -50544,7 +50544,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -50601,7 +50601,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -50658,7 +50658,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -50715,7 +50715,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -50772,7 +50772,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -50829,7 +50829,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">

--- a/Resumen/EstablecimientoSalud_resumen.xlsx
+++ b/Resumen/EstablecimientoSalud_resumen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>nombre_establecimiento</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
         </is>
@@ -19380,12 +19368,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>-7.164666</t>
+          <t>-7.16426544637534</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>-78.513279</t>
+          <t>-78.513159003721</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20064,12 +20052,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>-7.0993</t>
+          <t>-7.16496929581703</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>-78.58732</t>
+          <t>-78.5046072408526</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22458,12 +22446,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>-5.70956791</t>
+          <t>-5.70933993946857</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>-78.79767723</t>
+          <t>-78.7967521545297</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -28728,12 +28716,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>-12.06428378</t>
+          <t>-12.0643320849249</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>-75.20435799</t>
+          <t>-75.2046149207586</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32148,12 +32136,12 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>-10.7474554</t>
+          <t>-10.7424151045757</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>-77.7576531</t>
+          <t>-77.7660398115855</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -32205,12 +32193,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>-10.6962244</t>
+          <t>-10.7665798307641</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>-77.7757271</t>
+          <t>-77.7607787978902</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -41382,12 +41370,12 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>-16.0854612</t>
+          <t>-16.0744383</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>-69.6378272</t>
+          <t>-69.633933</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
